--- a/output/testing_result_databaru/evaluation_testing_60_40.xlsx
+++ b/output/testing_result_databaru/evaluation_testing_60_40.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,70 +429,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Jenis Rule</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Jenis Rule Label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Support Training</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Confidence Training</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lift Training</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Kategori Training</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Antecedent Support</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Consequent Support</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Lift</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Kategori Rule</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Count Antecedent</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Count Consequent</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Count Both</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Status Pengujian</t>
         </is>
@@ -509,50 +519,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>1.880952380952381</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.02781289506953224</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.0202275600505689</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2.273805246137262</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>22</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>253</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>16</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -569,50 +589,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.01772151898734177</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0.4375</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>1.3825</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.04298356510745891</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.2869785082174462</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.02149178255372946</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1.742290748898679</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>34</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>227</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>17</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -629,50 +659,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>1.940665154950869</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.02781289506953224</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.01517067003792667</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>1.705353934602946</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>22</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>253</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -689,50 +729,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>1.037653239929947</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.02275600505689001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.01517067003792667</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>1.456721915285451</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>18</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>362</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -749,50 +799,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.01350210970464135</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>0.4444444444444445</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1.393298059964727</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.01769911504424779</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.007585335018963337</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>1.339920948616601</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>14</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>253</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -809,50 +869,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.6190476190476191</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>1.284713535151364</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.01264222503160556</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.007585335018963337</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.6</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>1.311049723756906</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>362</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -869,50 +939,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>1.354285714285714</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.0404551201011378</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.2869785082174462</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.01517067003792667</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.375</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>1.306718061674009</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>32</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>227</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>12</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -929,50 +1009,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0.04388185654008439</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>0.611764705882353</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>1.26959925826723</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.05941845764854614</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.03539823008849557</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.5957446808510638</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>1.301751498765722</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>47</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>362</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>28</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -989,50 +1079,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>0.0219409282700422</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>0.5416666666666667</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>1.124124343257443</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.04298356510745891</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.02528445006321112</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>1.285342866428339</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>34</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>362</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>20</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1049,50 +1149,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>0.5416666666666667</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>1.698082010582011</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.02402022756005057</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.008849557522123894</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.3684210526315789</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>1.151861868109008</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>19</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>253</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>7</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1109,50 +1219,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>0.01518987341772152</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>0.5806451612903226</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>1.982894859161477</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.03666245259165613</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.3337547408343868</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.01390644753476612</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.3793103448275862</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>1.136494252873563</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>29</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>264</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1169,50 +1289,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>0.01687763713080169</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>0.5405405405405405</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>1.121787286410754</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.03413400758533502</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.01769911504424779</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>1.133005934110906</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>27</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>362</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>14</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1229,50 +1359,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.02109704641350211</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>0.7352941176470588</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>1.525960646955805</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.03666245259165613</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.01896333754740834</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.5172413793103449</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>1.130215279100781</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>29</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>362</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>15</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1289,50 +1429,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>0.05063291139240506</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>1.082768598187771</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.1099873577749684</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.05562579013906448</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.5057471264367817</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1.105099384009653</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>87</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>362</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>44</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1349,50 +1499,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>0.01434599156118144</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>0.6296296296296297</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>1.306674450282156</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.03286978508217446</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.01643489254108723</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>1.092541436464088</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>26</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>362</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>13</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1409,50 +1569,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>0.8</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>1.660245183887916</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>0.01011378002528445</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.005056890012642225</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>1.092541436464088</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>8</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>362</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1469,50 +1639,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.0219409282700422</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>0.4727272727272727</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>1.614356824731465</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.04551201011378003</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.3337547408343868</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.01643489254108723</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.3611111111111111</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>1.081965488215488</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>36</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>264</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>13</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1529,50 +1709,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>0.1544303797468354</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>0.4879999999999999</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>1.012749562171629</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.2869785082174462</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.1390644753476612</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.4845814977973568</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>1.058850731374887</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>227</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>362</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>110</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1589,50 +1779,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>0.1443037974683544</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>0.4927953890489913</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>1.02270146413845</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.3337547408343868</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.1592920353982301</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.4772727272727273</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>1.042880462079357</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>264</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>362</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>126</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1649,50 +1849,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>0.0160337552742616</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>0.5757575757575758</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>1.194873427798121</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.02149178255372946</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.01011378002528445</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.4705882352941176</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>1.028274293142671</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>17</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>362</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>8</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Konsisten</t>
         </is>
@@ -1709,50 +1919,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>0.4193548387096775</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>1.432090731616622</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.02654867256637168</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3337547408343868</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.008849557522123894</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9987373737373737</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>21</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>264</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>7</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1769,50 +1989,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>0.01772151898734177</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>0.4883720930232559</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>1.013521769233902</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>0.04551201011378003</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.0202275600505689</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.9711479435236341</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>36</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>362</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>16</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1829,50 +2059,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>0.6</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>1.245183887915937</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0.02275600505689001</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.01011378002528445</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.4444444444444444</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.9711479435236341</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>18</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>362</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>8</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1889,50 +2129,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>0.5416666666666667</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>1.124124343257443</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0.02402022756005057</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.01011378002528445</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.4210526315789473</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.9200348938644954</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>19</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>362</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>8</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -1949,50 +2199,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>1.185889417062797</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0.01264222503160556</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.005056890012642225</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.4</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.8740331491712707</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>10</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>362</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>4</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2009,50 +2269,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>0.02953586497890295</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>0.4069767441860466</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>1.275839793281654</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.05056890012642225</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.01390644753476612</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.275</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.8597826086956523</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>40</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>253</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>11</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2069,50 +2339,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>0.4615384615384615</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>1.446886446886447</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0.01390644753476612</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.003792667509481669</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.8526769673014732</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>11</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>253</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>3</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2129,50 +2409,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
         <v>0.01350210970464135</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>0.5925925925925926</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>1.229811247324382</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0.02528445006321112</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.008849557522123894</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.35</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.7647790055248618</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>20</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>362</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>7</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2189,50 +2479,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>2.33656908842712</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>0.01011378002528445</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3337547408343868</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.002528445006321113</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.25</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.7490530303030304</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>8</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>264</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2249,50 +2549,60 @@
           <t>operator_Indah</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>0.01181434599156118</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>0.4242424242424243</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>1.32996632996633</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>0.02149178255372946</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.3198482932996207</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.005056890012642225</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.2352941176470588</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.7356428737502907</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>17</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>253</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>4</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2309,50 +2619,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>0.01181434599156118</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>0.4827586206896551</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>1.001872093725467</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0.01643489254108723</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.005056890012642225</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.3076923076923077</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.6723331916702082</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>13</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>362</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>4</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2369,50 +2689,60 @@
           <t>operator_Riska</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>0.4615384615384615</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>1.576147195743737</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0.02528445006321112</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.3337547408343868</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.005056890012642225</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.2</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.5992424242424244</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>20</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>264</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2429,50 +2759,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>0.52</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>1.079159369527146</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.02781289506953224</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.007585335018963337</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.5959316926167755</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>22</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>362</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>6</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2489,50 +2829,60 @@
           <t>waktu_Pagi</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>0.0109704641350211</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>0.5</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>1.669014084507042</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.01643489254108723</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.2844500632111251</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.002528445006321113</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.5408547008547009</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>13</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>225</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>2</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2549,50 +2899,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>0.01518987341772152</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>1.131985352650852</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>0.0316055625790139</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.007585335018963337</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.24</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.5244198895027624</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>25</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>362</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>6</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2609,50 +2969,60 @@
           <t>waktu_Siang</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>0.01012658227848101</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>1.245183887915937</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>0.01643489254108723</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.4576485461441214</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.002528445006321113</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.3361665958351041</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>13</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>362</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>2</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>
@@ -2669,50 +3039,60 @@
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>0.01350210970464135</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>0.4848484848484849</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>1.532121212121212</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Moderate Pattern</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.02149178255372946</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.2869785082174462</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>Weak Pattern</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>17</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>227</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>Tidak Konsisten</t>
         </is>

--- a/output/testing_result_databaru/evaluation_testing_60_40.xlsx
+++ b/output/testing_result_databaru/evaluation_testing_60_40.xlsx
@@ -511,66 +511,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>produk_paket radian brightening ultimate</t>
+          <t>produk_glowtech spicule rejuvenation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>operator_Indah</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>produk_operator</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Produk × Operator</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.01012658227848101</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>1.880952380952381</v>
+        <v>1.185889417062797</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.001589825119236884</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4451510333863275</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.001589825119236884</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.246428571428571</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Strong Pattern</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>0.02781289506953224</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3198482932996207</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.0202275600505689</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.273805246137262</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Strong Pattern</t>
-        </is>
-      </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>253</v>
+        <v>840</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -581,12 +581,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>produk_paket radiant brightening ultimate</t>
+          <t>produk_paket radian brightening ultimate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>operator_Oktavira</t>
+          <t>operator_Indah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -600,47 +600,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.01772151898734177</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4375</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3825</v>
+        <v>1.880952380952381</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.04298356510745891</v>
+        <v>0.01483836777954425</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2869785082174462</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02149178255372946</v>
+        <v>0.008479067302596715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M3" t="n">
-        <v>1.742290748898679</v>
+        <v>1.888416312234175</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
-        <v>227</v>
+        <v>571</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -651,52 +651,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>produk_paket acne brightening</t>
+          <t>produk_night cream brightening, waktu_Pagi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>operator_Indah</t>
+          <t>operator_Oktavira</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>produk_operator</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Produk × Operator</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0109704641350211</v>
+        <v>0.01350210970464135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="G4" t="n">
-        <v>1.940665154950869</v>
+        <v>1.532121212121212</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.02781289506953224</v>
+        <v>0.009009009009009009</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3198482932996207</v>
+        <v>0.3078961314255432</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01517067003792667</v>
+        <v>0.004239533651298357</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="M4" t="n">
-        <v>1.705353934602946</v>
+        <v>1.528399311531842</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -704,13 +704,13 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P4" t="n">
-        <v>253</v>
+        <v>581</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -721,12 +721,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>operator_Oktavira, produk_radian brightening ultimate</t>
+          <t>produk_sunscreen oily acne new, waktu_Malam</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Indah</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.01012658227848101</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="G5" t="n">
-        <v>1.037653239929947</v>
+        <v>1.446886446886447</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -754,33 +754,33 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.02275600505689001</v>
+        <v>0.01165871754107048</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01517067003792667</v>
+        <v>0.005299417064122946</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="M5" t="n">
-        <v>1.456721915285451</v>
+        <v>1.502149339277185</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
-        <v>362</v>
+        <v>571</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>produk_sunscreen oily acne new, waktu_Siang</t>
+          <t>produk_paket custom</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -801,22 +801,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>produk_operator</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Produk × Operator</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.01350210970464135</v>
+        <v>0.0109704641350211</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4444444444444445</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>1.393298059964727</v>
+        <v>1.698082010582011</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.01769911504424779</v>
+        <v>0.02649708532061473</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3198482932996207</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007585335018963337</v>
+        <v>0.01112877583465819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.339920948616601</v>
+        <v>1.387985989492119</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="P6" t="n">
-        <v>253</v>
+        <v>571</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -861,22 +861,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>produk_brightening cream 1 with licorice plus astaxanthin</t>
+          <t>produk_paket acne brightening</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Indah</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -886,77 +886,77 @@
         <v>0.6190476190476191</v>
       </c>
       <c r="G7" t="n">
-        <v>1.284713535151364</v>
+        <v>1.940665154950869</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.01264222503160556</v>
+        <v>0.01218865924748278</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007585335018963337</v>
+        <v>0.004769475357710651</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="M7" t="n">
-        <v>1.311049723756906</v>
+        <v>1.293154648595142</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Weak Pattern</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="P7" t="n">
-        <v>362</v>
+        <v>571</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Konsisten</t>
+          <t>Tidak Konsisten</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>produk_radian brightening ultimate, waktu_Siang</t>
+          <t>operator_Anisa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>operator_Oktavira</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>operator_waktu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Operator × Waktu</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.04388185654008439</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.611764705882353</v>
       </c>
       <c r="G8" t="n">
-        <v>1.354285714285714</v>
+        <v>1.26959925826723</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -964,44 +964,44 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.0404551201011378</v>
+        <v>0.09591944886062533</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2869785082174462</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01517067003792667</v>
+        <v>0.05511393746687864</v>
       </c>
       <c r="L8" t="n">
-        <v>0.375</v>
+        <v>0.574585635359116</v>
       </c>
       <c r="M8" t="n">
-        <v>1.306718061674009</v>
+        <v>1.290765588003157</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Weak Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="P8" t="n">
-        <v>227</v>
+        <v>840</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Tidak Konsisten</t>
+          <t>Konsisten</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>operator_Anisa</t>
+          <t>produk_dna salmon extra marine collagen and hyaluronic acid 30 ml</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1011,56 +1011,56 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>operator_waktu</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Operator × Waktu</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04388185654008439</v>
+        <v>0.02109704641350211</v>
       </c>
       <c r="F9" t="n">
-        <v>0.611764705882353</v>
+        <v>0.7352941176470588</v>
       </c>
       <c r="G9" t="n">
-        <v>1.26959925826723</v>
+        <v>1.525960646955805</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.05941845764854614</v>
+        <v>0.0302066772655008</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03539823008849557</v>
+        <v>0.01642819289878113</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.543859649122807</v>
       </c>
       <c r="M9" t="n">
-        <v>1.301751498765722</v>
+        <v>1.221741854636591</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="P9" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>produk_paket radiant brightening ultimate</t>
+          <t>operator_Riska, produk_night cream brightening</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0219409282700422</v>
+        <v>0.01434599156118144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="G10" t="n">
-        <v>1.124124343257443</v>
+        <v>1.306674450282156</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.04298356510745891</v>
+        <v>0.0100688924218336</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02528445006321112</v>
+        <v>0.005299417064122946</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="M10" t="n">
-        <v>1.285342866428339</v>
+        <v>1.182330827067669</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="P10" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1141,32 +1141,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>produk_paket custom</t>
+          <t>operator_Riska</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>operator_Indah</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>produk_operator</t>
+          <t>operator_waktu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Produk × Operator</t>
+          <t>Operator × Waktu</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0109704641350211</v>
+        <v>0.1443037974683544</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.4927953890489913</v>
       </c>
       <c r="G11" t="n">
-        <v>1.698082010582011</v>
+        <v>1.02270146413845</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1174,114 +1174,114 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.02402022756005057</v>
+        <v>0.2935877053524112</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3198482932996207</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008849557522123894</v>
+        <v>0.151033386327504</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.5144404332129964</v>
       </c>
       <c r="M11" t="n">
-        <v>1.151861868109008</v>
+        <v>1.155653687467767</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Weak Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>554</v>
       </c>
       <c r="P11" t="n">
-        <v>253</v>
+        <v>840</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>285</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Tidak Konsisten</t>
+          <t>Konsisten</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>produk_serum brightening glowing</t>
+          <t>produk_milk cleanser 110 ml</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>operator_Riska</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>produk_operator</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Produk × Operator</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.01518987341772152</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>1.982894859161477</v>
+        <v>1.245183887915937</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.03666245259165613</v>
+        <v>0.01854795972443031</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3337547408343868</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01390644753476612</v>
+        <v>0.009538950715421303</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="M12" t="n">
-        <v>1.136494252873563</v>
+        <v>1.15530612244898</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Weak Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="P12" t="n">
-        <v>264</v>
+        <v>840</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Tidak Konsisten</t>
+          <t>Konsisten</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>produk_sunscreen glowing new</t>
+          <t>produk_paket custom</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.01687763713080169</v>
+        <v>0.0109704641350211</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5405405405405405</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>1.121787286410754</v>
+        <v>1.124124343257443</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.03413400758533502</v>
+        <v>0.02649708532061473</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01769911504424779</v>
+        <v>0.01324854266030737</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.133005934110906</v>
+        <v>1.123214285714286</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>produk_dna salmon extra marine collagen and hyaluronic acid 30 ml</t>
+          <t>produk_acne cream 2 new</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1370,33 +1370,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.02109704641350211</v>
+        <v>0.01012658227848101</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7352941176470588</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.525960646955805</v>
+        <v>1.245183887915937</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.03666245259165613</v>
+        <v>0.01165871754107048</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01896333754740834</v>
+        <v>0.005829358770535241</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>1.130215279100781</v>
+        <v>1.123214285714286</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P14" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>produk_night cream brightening</t>
+          <t>produk_bb chusion flawless</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.05063291139240506</v>
+        <v>0.01181434599156118</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4827586206896551</v>
       </c>
       <c r="G15" t="n">
-        <v>1.082768598187771</v>
+        <v>1.001872093725467</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.1099873577749684</v>
+        <v>0.008479067302596715</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05562579013906448</v>
+        <v>0.004239533651298357</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5057471264367817</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>1.105099384009653</v>
+        <v>1.123214285714286</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>operator_Riska, produk_night cream brightening</t>
+          <t>produk_hb night brightening</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01434599156118144</v>
+        <v>0.01350210970464135</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="G16" t="n">
-        <v>1.306674450282156</v>
+        <v>1.229811247324382</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.03286978508217446</v>
+        <v>0.007419183889772125</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01643489254108723</v>
+        <v>0.003709591944886063</v>
       </c>
       <c r="L16" t="n">
         <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>1.092541436464088</v>
+        <v>1.123214285714286</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="P16" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1561,82 +1561,82 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>operator_Riska, produk_daily ceramois hydra gel</t>
+          <t>produk_hb night yellow plus licorice</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Indah</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>produk_operator</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Produk × Operator</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01012658227848101</v>
+        <v>0.01181434599156118</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8</v>
+        <v>0.4242424242424243</v>
       </c>
       <c r="G17" t="n">
-        <v>1.660245183887916</v>
+        <v>1.32996632996633</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.01011378002528445</v>
+        <v>0.01112877583465819</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K17" t="n">
-        <v>0.005056890012642225</v>
+        <v>0.003709591944886063</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>1.092541436464088</v>
+        <v>1.101576182136602</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Weak Pattern</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="P17" t="n">
-        <v>362</v>
+        <v>571</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Konsisten</t>
+          <t>Tidak Konsisten</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>produk_facial wash oily acne 110 ml new</t>
+          <t>produk_paket radiant brightening ultimate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>operator_Riska</t>
+          <t>operator_Oktavira</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0219409282700422</v>
+        <v>0.01772151898734177</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4727272727272727</v>
+        <v>0.4375</v>
       </c>
       <c r="G18" t="n">
-        <v>1.614356824731465</v>
+        <v>1.3825</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.04551201011378003</v>
+        <v>0.01748807631160572</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3337547408343868</v>
+        <v>0.3078961314255432</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01643489254108723</v>
+        <v>0.005829358770535241</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>1.081965488215488</v>
+        <v>1.082616179001721</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1684,13 +1684,13 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P18" t="n">
-        <v>264</v>
+        <v>581</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1701,32 +1701,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>produk_radian brightening ultimate, waktu_Siang</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>operator_Oktavira</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>waktu_Siang</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>operator_waktu</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Operator × Waktu</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.1544303797468354</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4879999999999999</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="G19" t="n">
-        <v>1.012749562171629</v>
+        <v>1.354285714285714</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1734,44 +1734,44 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2869785082174462</v>
+        <v>0.01589825119236884</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.3078961314255432</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1390644753476612</v>
+        <v>0.005299417064122946</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4845814977973568</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M19" t="n">
-        <v>1.058850731374887</v>
+        <v>1.082616179001721</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Weak Pattern</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
-        <v>362</v>
+        <v>581</v>
       </c>
       <c r="Q19" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Konsisten</t>
+          <t>Tidak Konsisten</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>operator_Riska</t>
+          <t>operator_Riska, produk_daily ceramois hydra gel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>operator_waktu</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Operator × Waktu</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.1443037974683544</v>
+        <v>0.01012658227848101</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4927953890489913</v>
+        <v>0.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.02270146413845</v>
+        <v>1.660245183887916</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.3337547408343868</v>
+        <v>0.01324854266030737</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1592920353982301</v>
+        <v>0.006359300476947536</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.48</v>
       </c>
       <c r="M20" t="n">
-        <v>1.042880462079357</v>
+        <v>1.078285714285714</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="P20" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q20" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1841,32 +1841,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>produk_hb night yellow plus licorice</t>
+          <t>produk_facial wash oily acne 110 ml new</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Riska</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0160337552742616</v>
+        <v>0.0219409282700422</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="G21" t="n">
-        <v>1.194873427798121</v>
+        <v>1.614356824731465</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1874,69 +1874,69 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.02149178255372946</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.2935877053524112</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01011378002528445</v>
+        <v>0.01218865924748278</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.3108108108108108</v>
       </c>
       <c r="M21" t="n">
-        <v>1.028274293142671</v>
+        <v>1.058664259927798</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Weak Pattern</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="P21" t="n">
-        <v>362</v>
+        <v>554</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Konsisten</t>
+          <t>Tidak Konsisten</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>produk_paket acne 1</t>
+          <t>produk_paket radiant brightening ultimate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>operator_Riska</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>produk_operator</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Produk × Operator</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0109704641350211</v>
+        <v>0.0219409282700422</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4193548387096775</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>1.432090731616622</v>
+        <v>1.124124343257443</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1944,37 +1944,37 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.02654867256637168</v>
+        <v>0.01748807631160572</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3337547408343868</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K22" t="n">
-        <v>0.008849557522123894</v>
+        <v>0.007949125596184419</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9987373737373737</v>
+        <v>1.021103896103896</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Weak Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="P22" t="n">
-        <v>264</v>
+        <v>840</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Tidak Konsisten</t>
+          <t>Konsisten</t>
         </is>
       </c>
     </row>
@@ -2014,44 +2014,44 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.04551201011378003</v>
+        <v>0.0201377848436672</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0202275600505689</v>
+        <v>0.009009009009009009</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9711479435236341</v>
+        <v>1.004981203007519</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Weak Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P23" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Tidak Konsisten</t>
+          <t>Konsisten</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>produk_milk cleanser 110 ml</t>
+          <t>produk_night cream brightening</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.05063291139240506</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="G24" t="n">
-        <v>1.245183887915937</v>
+        <v>1.082768598187771</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2084,19 +2084,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.02275600505689001</v>
+        <v>0.04769475357710652</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K24" t="n">
-        <v>0.01011378002528445</v>
+        <v>0.02119766825649179</v>
       </c>
       <c r="L24" t="n">
         <v>0.4444444444444444</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9711479435236341</v>
+        <v>0.9984126984126984</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="P24" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2121,32 +2121,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>produk_paket custom</t>
+          <t>produk_sunscreen oily acne new</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Indah</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0109704641350211</v>
+        <v>0.02953586497890295</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.4069767441860466</v>
       </c>
       <c r="G25" t="n">
-        <v>1.124124343257443</v>
+        <v>1.275839793281654</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2154,19 +2154,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.02402022756005057</v>
+        <v>0.04610492845786963</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01011378002528445</v>
+        <v>0.01377848436671966</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.2988505747126437</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9200348938644954</v>
+        <v>0.9876200253638504</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="P25" t="n">
-        <v>362</v>
+        <v>571</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2191,32 +2191,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>produk_glowtech spicule rejuvenation</t>
+          <t>produk_daily ceramois hydra gel, waktu_Siang</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Riska</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>0.01012658227848101</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="G26" t="n">
-        <v>1.185889417062797</v>
+        <v>1.576147195743737</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2224,19 +2224,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.01264222503160556</v>
+        <v>0.02331743508214097</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.2935877053524112</v>
       </c>
       <c r="K26" t="n">
-        <v>0.005056890012642225</v>
+        <v>0.006359300476947536</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8740331491712707</v>
+        <v>0.928946504758779</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="P26" t="n">
-        <v>362</v>
+        <v>554</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2261,32 +2261,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>produk_sunscreen oily acne new</t>
+          <t>produk_night cream acne brightening</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>operator_Indah</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>produk_operator</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Produk × Operator</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.02953586497890295</v>
+        <v>0.01518987341772152</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4069767441860466</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="G27" t="n">
-        <v>1.275839793281654</v>
+        <v>1.131985352650852</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2294,19 +2294,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.05056890012642225</v>
+        <v>0.01430842607313196</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3198482932996207</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01390644753476612</v>
+        <v>0.005829358770535241</v>
       </c>
       <c r="L27" t="n">
-        <v>0.275</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8597826086956523</v>
+        <v>0.9152116402116401</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="P27" t="n">
-        <v>253</v>
+        <v>840</v>
       </c>
       <c r="Q27" t="n">
         <v>11</v>
@@ -2331,32 +2331,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>produk_sunscreen oily acne new, waktu_Malam</t>
+          <t>operator_Oktavira</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>operator_Indah</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>operator_waktu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Operator × Waktu</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.01012658227848101</v>
+        <v>0.1544303797468354</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.4879999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>1.446886446886447</v>
+        <v>1.012749562171629</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.01390644753476612</v>
+        <v>0.3078961314255432</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3198482932996207</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K28" t="n">
-        <v>0.003792667509481669</v>
+        <v>0.1197668256491786</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3889845094664372</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8526769673014732</v>
+        <v>0.8738259159085322</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>11</v>
+        <v>581</v>
       </c>
       <c r="P28" t="n">
-        <v>253</v>
+        <v>840</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>226</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2401,32 +2401,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>produk_hb night brightening</t>
+          <t>produk_sunscreen oily acne new, waktu_Siang</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Indah</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>0.01350210970464135</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="G29" t="n">
-        <v>1.229811247324382</v>
+        <v>1.393298059964727</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2434,19 +2434,19 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.02528445006321112</v>
+        <v>0.02225755166931637</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.3025967143614203</v>
       </c>
       <c r="K29" t="n">
-        <v>0.008849557522123894</v>
+        <v>0.005829358770535241</v>
       </c>
       <c r="L29" t="n">
-        <v>0.35</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7647790055248618</v>
+        <v>0.8655241431073305</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="P29" t="n">
-        <v>362</v>
+        <v>571</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2471,12 +2471,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>produk_facial wash oily acne 110 ml new, waktu_Pagi</t>
+          <t>operator_Riska, produk_facial wash oily acne 110 ml new</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>operator_Riska</t>
+          <t>waktu_Pagi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2493,30 +2493,30 @@
         <v>0.0109704641350211</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>2.33656908842712</v>
+        <v>1.669014084507042</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Strong Pattern</t>
+          <t>Moderate Pattern</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.01011378002528445</v>
+        <v>0.01218865924748278</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3337547408343868</v>
+        <v>0.3015368309485957</v>
       </c>
       <c r="K30" t="n">
-        <v>0.002528445006321113</v>
+        <v>0.003179650238473768</v>
       </c>
       <c r="L30" t="n">
-        <v>0.25</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7490530303030304</v>
+        <v>0.865133338427447</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="P30" t="n">
-        <v>264</v>
+        <v>569</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>produk_hb night yellow plus licorice</t>
+          <t>produk_serum brightening glowing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>operator_Indah</t>
+          <t>operator_Riska</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2560,33 +2560,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.01181434599156118</v>
+        <v>0.01518987341772152</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="G31" t="n">
-        <v>1.32996632996633</v>
+        <v>1.982894859161477</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.02149178255372946</v>
+        <v>0.0296767355590885</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3198482932996207</v>
+        <v>0.2935877053524112</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005056890012642225</v>
+        <v>0.007419183889772125</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.25</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7356428737502907</v>
+        <v>0.8515342960288809</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="P31" t="n">
-        <v>253</v>
+        <v>554</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>produk_bb chusion flawless</t>
+          <t>produk_sunscreen glowing new</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.01181434599156118</v>
+        <v>0.01687763713080169</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4827586206896551</v>
+        <v>0.5405405405405405</v>
       </c>
       <c r="G32" t="n">
-        <v>1.001872093725467</v>
+        <v>1.121787286410754</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.01643489254108723</v>
+        <v>0.03232644409114997</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K32" t="n">
-        <v>0.005056890012642225</v>
+        <v>0.01218865924748278</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6723331916702082</v>
+        <v>0.8470140515222482</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2664,13 +2664,13 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="P32" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2681,12 +2681,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>produk_daily ceramois hydra gel, waktu_Siang</t>
+          <t>operator_Oktavira, produk_radian brightening ultimate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>operator_Riska</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.01012658227848101</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1.576147195743737</v>
+        <v>1.037653239929947</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2714,19 +2714,19 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.02528445006321112</v>
+        <v>0.01430842607313196</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3337547408343868</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K33" t="n">
-        <v>0.005056890012642225</v>
+        <v>0.005299417064122946</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5992424242424244</v>
+        <v>0.832010582010582</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P33" t="n">
-        <v>264</v>
+        <v>840</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2784,19 +2784,19 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.02781289506953224</v>
+        <v>0.01483836777954425</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K34" t="n">
-        <v>0.007585335018963337</v>
+        <v>0.005299417064122946</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5959316926167755</v>
+        <v>0.8022959183673469</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P34" t="n">
-        <v>362</v>
+        <v>840</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2821,32 +2821,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>operator_Riska, produk_facial wash oily acne 110 ml new</t>
+          <t>produk_brightening cream 1 with licorice plus astaxanthin</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>waktu_Pagi</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>0.0109704641350211</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="G35" t="n">
-        <v>1.669014084507042</v>
+        <v>1.284713535151364</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2854,19 +2854,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.01643489254108723</v>
+        <v>0.009009009009009009</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2844500632111251</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K35" t="n">
-        <v>0.002528445006321113</v>
+        <v>0.003179650238473768</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5408547008547009</v>
+        <v>0.7928571428571429</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P35" t="n">
-        <v>225</v>
+        <v>840</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2891,32 +2891,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>produk_night cream acne brightening</t>
+          <t>produk_paket acne 1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Riska</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.01518987341772152</v>
+        <v>0.0109704641350211</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4193548387096775</v>
       </c>
       <c r="G36" t="n">
-        <v>1.131985352650852</v>
+        <v>1.432090731616622</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2924,19 +2924,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.0316055625790139</v>
+        <v>0.03179650238473768</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.2935877053524112</v>
       </c>
       <c r="K36" t="n">
-        <v>0.007585335018963337</v>
+        <v>0.00688924218335983</v>
       </c>
       <c r="L36" t="n">
-        <v>0.24</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5244198895027624</v>
+        <v>0.7379963898916968</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="P36" t="n">
-        <v>362</v>
+        <v>554</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -2961,52 +2961,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>produk_acne cream 2 new</t>
+          <t>produk_facial wash oily acne 110 ml new, waktu_Pagi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>waktu_Siang</t>
+          <t>operator_Riska</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>produk_waktu</t>
+          <t>produk_operator_waktu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Produk × Waktu</t>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.01012658227848101</v>
+        <v>0.0109704641350211</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="G37" t="n">
-        <v>1.245183887915937</v>
+        <v>2.33656908842712</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Moderate Pattern</t>
+          <t>Strong Pattern</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.01643489254108723</v>
+        <v>0.01483836777954425</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4576485461441214</v>
+        <v>0.2935877053524112</v>
       </c>
       <c r="K37" t="n">
-        <v>0.002528445006321113</v>
+        <v>0.003179650238473768</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3361665958351041</v>
+        <v>0.7298865394533264</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="P37" t="n">
-        <v>362</v>
+        <v>554</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -3031,32 +3031,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>produk_night cream brightening, waktu_Pagi</t>
+          <t>produk_hb night yellow plus licorice</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>operator_Oktavira</t>
+          <t>waktu_Siang</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>produk_operator_waktu</t>
+          <t>produk_waktu</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Produk × Operator × Waktu</t>
+          <t>Produk × Waktu</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01350210970464135</v>
+        <v>0.0160337552742616</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="G38" t="n">
-        <v>1.532121212121212</v>
+        <v>1.194873427798121</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3064,19 +3064,19 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.02149178255372946</v>
+        <v>0.01112877583465819</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2869785082174462</v>
+        <v>0.4451510333863275</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.002649708532061473</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.5348639455782312</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -3084,13 +3084,13 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P38" t="n">
-        <v>227</v>
+        <v>840</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
